--- a/AAII_Financials/Yearly/CWEN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CWEN_YR_FIN.xlsx
@@ -2174,7 +2174,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>728000</v>
+        <v>734000</v>
       </c>
       <c r="E58" s="3">
         <v>440000</v>
@@ -2207,7 +2207,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>52000</v>
+        <v>46000</v>
       </c>
       <c r="E59" s="3">
         <v>56000</v>
